--- a/data/labels/label_template.xlsx
+++ b/data/labels/label_template.xlsx
@@ -496,12 +496,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>교통약자 이동편의 증진(국고)</t>
+          <t>교통문화 질서확립</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>노상주차장 및 노면표시 설치 및 유지보수</t>
+          <t>교통행정 운영지원</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>자동차관리법 업무추진</t>
+          <t>시일원 차선도색 공사</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>어린이보호구역 정비사업</t>
+          <t>교통사고 잦은곳 개선사업</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>부산-김해간 경전철운영</t>
+          <t>시책추진업무추진비</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>화명동 산성로 초입 회전교차로 설치 사업</t>
+          <t>어린이 등하교 교통안전지도</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>어린이보호구역 방호울타리 설치('23년 재난안전특별교부세 포함)</t>
+          <t>자동차등록관리</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>보행환경 개선</t>
+          <t>녹지 내 안전한 보행공간 마련 및 환경개선사업</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>선박(여객선,도선,자치선) 지원</t>
+          <t>시내버스 어린이 100원 요금제 손실보전</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>도시계획도로 신호등 설치공사</t>
+          <t>소양 소로3-2호선 도로개설사업</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>영흥면 진두항 보행자도로 개설공사</t>
+          <t>신천동 82-4~74-2번지 미끄럼방지포장공사(시 주민참여예산 동참여형 사업)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>도로제설</t>
+          <t>부설주차장 위탁관리</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>농어촌도로 유지관리</t>
+          <t>북아현 과선교(도로교,녹지교) 설치공사</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>청송IC접속부 국도31호선 확장공사</t>
+          <t>판문동 15통 현대아파트 주변 도시계획도로 개설</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>금주1교 재가설 공사</t>
+          <t>북원로(시청사거리~만대사거리) 보도정비공사</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>특별교통수단 도입보조(보조)</t>
+          <t>알뜰교통카드연계마일리지지원</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>공공형택시(희망택시) 재정지원</t>
+          <t>교통개선</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>지방도 비점오염저감사업(시설설치)(기금/직접)</t>
+          <t>가로등 조도 및 에너지 효율 개선</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>예탁금</t>
+          <t>불법주정차 지도단속</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>수소차 구매 지원</t>
+          <t>(도비보조)전기자동차 완속충전기 설치 지원사업</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>농촌형 교통모델 사업(공공형 택시)</t>
+          <t>공영주차장 관리</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>사천시 생활밀착형 국민체육센터 진입도로 확장공사</t>
+          <t>농촌 왕진버스 지원</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>문화및관광</t>
+          <t>농림해양수산</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>체육</t>
+          <t>농업ㆍ농촌</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>교통질서관리</t>
+          <t>송파공영차고지 정비 및 세차동 이전 공사</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>장애인 전동보장구 충전기 설치사업</t>
+          <t>장애인 생활이동지원센터 운영지원</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>비점오염저감시설 유지관리</t>
+          <t>보령-대전 고속도로 건설 사전타당성조사</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>포항 캐릭터해상공원 관리</t>
+          <t>항만정책</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>유가 유곡2리 도시계획도로 개설</t>
+          <t>내서 평성마을 도시계획도로(소로2-25호선) 개설공사</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>버스공영차고지지원사업</t>
+          <t>주정차위반 과태료 부과 및 징수관리</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>공항활성화 업무추진</t>
+          <t>드론시스템 관리</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>견인보관소 위탁운영</t>
+          <t>찾아가는 어르신 교통안전교실 운영</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>도로환경 개선(용인시 관내)</t>
+          <t>도로반사경 설치 및 유지관리</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>이촌지하차도 조명등 교체(구 주민참여)</t>
+          <t>위원회 관리</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>연동교 교량받침 교체공사('24년 특별교부세 사업)</t>
+          <t>동면 가산리 LED등기구 교체공사</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>창촌리 우회도로 연결 소교량 설치공사</t>
+          <t>도)주민숙원도로사업(지역현안도로사업)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>특별교통수단 도입보조(국고)</t>
+          <t>내부거래 지출</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>입암동 투썸플레이스~장난감도서관 도로개설</t>
+          <t>입암동 월대산 뒤 도로개설</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>법규 위반자 단속 및 처리</t>
+          <t>예비비(교통사업특별회계)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>동탄권 장애인 전용 주차구역 단속</t>
+          <t>지방하천 법면확장보도 유지관리사업(자체)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>사회복지</t>
+          <t>국토및지역개발</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>사회복지일반</t>
+          <t>수자원</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>앙성 양촌마을(군도13호선)진입로 확포장</t>
+          <t>도시계획시설부지 매수청구</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>자동차전용도로 구조체 안전점검 및 보수보강</t>
+          <t>노상적치물 정비</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>도로(차도, 인도) 정비 및 긴급보수(시 주민참여예산 지역참여형 사업)</t>
+          <t>방촌동 용호초교 동편 도로건설</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>광역버스정보시스템(BIS)구축사업</t>
+          <t>논공 남1리 마을공영 주차장 조성</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>녹색주차마을 조성</t>
+          <t>대중교통이용활성화</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>택시감차 지원</t>
+          <t>(자체사업)자전거 이용 활성화</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>적자노선 재정지원</t>
+          <t>교통약자 이동지원센터 운영(국비/지원)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>청주 다목적 실내체육관 교통영향평가 이행사업</t>
+          <t>태양광충전식농업기계용배터리커버보급</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>문화및관광</t>
+          <t>농림해양수산</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>체육</t>
+          <t>농업ㆍ농촌</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>밀양무안-신법간 도로건설</t>
+          <t>미불용지보상</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[도]전세버스사각지대충돌예방장치설치지원</t>
+          <t>여성안심터미널 사업</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>내부거래지출</t>
+          <t>어린이 보호구역 개선(도민참여)(전환사업)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>무단방치 이륜차 견인</t>
+          <t>벽지노선 지원사업(국고)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>지능형 교통정보 시스템 사업</t>
+          <t>브랜드콜 통합 지원 사업</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>도시철도 건설 지원</t>
+          <t>초지역 환승센터(환승주차장) 조성</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>도로긴급정비 및 보수사업</t>
+          <t>상정~환희간 도로확포장공사</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>차량등록처리 내실화</t>
+          <t>전라남도 택시 감차위원회 운영</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>교통사고 잦은 곳 개선(전환사업)</t>
+          <t>저상버스 지원</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>화산도시계획도로 소로1-23호선 개설공사</t>
+          <t>교통약자 교통안전 위탁교육 운영</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>도로점용 허가관리</t>
+          <t>도로명주소 시설물 관리</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>어린이보호구역유지관리</t>
+          <t>재전마을 진입도로(소로1-555호선) 도로개설</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>드론 산업 활성화</t>
+          <t>가덕도신공항 보상 추진</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>운수교 내진성능 보강공사</t>
+          <t>중리동로보행자우선도로조성사업</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>스쿨존 무인교통단속장비 운영(전환)</t>
+          <t>수소차 보급</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>공공질서및안전</t>
+          <t>산업ㆍ중소기업및에너지</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>경찰</t>
+          <t>에너지및자원개발</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>도로명 및 건물번호 활용(새주소 부여사업)</t>
+          <t>도로명 및 건물번호 활용</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>자전거도시 브랜드화 지원사업</t>
+          <t>포장도 유지관리 사업</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>인평3리 도시계획도로 정비(소2-3)</t>
+          <t>공동주택 단지내도로 교통안전 실태점검</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>도로명주소정보사업</t>
+          <t>중학동(고상아리,소로3-49호) 도시계획도로개설사업</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>여객 경영실태 분석</t>
+          <t>국제크루즈,페리선 유치</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>지능형 교통시스템(ITS,BIS) 구축</t>
+          <t>지하철 역사 에스컬레이터 안전부품 설치 지원</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>세수증대활동비</t>
+          <t>자율주행기반 미래형 ITS 구축</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>하빈 묘1리 도채마을 진입로 확포장</t>
+          <t>하빈 동곡2리(동곡농협 뒷편)도시계획도로 개설</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>공공자전거 운영 및 확충</t>
+          <t>교통사고 잦은 곳 개선사업(전환사업)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>도로굴착 복구공사</t>
+          <t>예덕선(성연면 명천리) 농어촌도로 확포장공사</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>하소동 736일원 구거 복개(1단계 전환사업)</t>
+          <t>교량 및 시설물 유지관리</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>지능형교통체계(ITS) 구축사업</t>
+          <t>주민참여 감독자 일비</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>광역버스 입석대책에 따른 재정지원</t>
+          <t>농촌형교통모델 공공형버스</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>덕암로 보행자 도로정비</t>
+          <t>에나교 일원 ~ 대곡중 방면 옹벽 정비공사</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>대정 도시계획도로(대로3-2-1호선) 개설사업</t>
+          <t>도로명주소정착추진(보조)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>장림동 벽산아파트 일원 보도설치공사</t>
+          <t>서곶로 봉수초 보행자전용도로 일원 열선 설치</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>도시계획도로 보상</t>
+          <t>김제 귀신사 우회도로 개설사업(특별조정교부금)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>광역도로 도로명판 설치</t>
+          <t>연천도시계획도로 중2-19호선 개설공사(자체)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>인력운영비(주차장특별회계)</t>
+          <t>부서운영경비(교통과)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>중앙탑 군도11호선(잣고개) 선형개량</t>
+          <t>이반성 수성마을 안길정비공사</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>노인·장애인보호구역 정비</t>
+          <t>바우처 택시 사업(도비)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>장애인생활이동지원센터 종사자 특별수당지원</t>
+          <t>장애인 전동보장구 급속충전기 설치</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>현풍 자모리 374번지선 마을안길정비</t>
+          <t>진례 테크노밸리 우회도로 개설</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>자동차 정기검사 미이행자 관리</t>
+          <t>차선도색</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GTX-A 킨텍스역 임시 환승주차장 조성사업</t>
+          <t>보조금반환금</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>장애인콜택시 운영비 보조사업</t>
+          <t>차량특사경 업무추진</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>장애인생활체육지도자교통비지원</t>
+          <t>침수우려 취약도로 자동차단시설 설치</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>문화및관광</t>
+          <t>공공질서및안전</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>체육</t>
+          <t>재난방재ㆍ민방위</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>도로명 안내 도로표지판 교체설치(시민참여)</t>
+          <t>섬주민여객선운임지원(보조)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>공영주차장 관리</t>
+          <t>차량등록업무 추진</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>월광2,3주차장 CCTV 설치(주민참여예산)</t>
+          <t>평동로 무인교통단속장비 설치사업</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>스마트 버스정류장 시설 개선 사업</t>
+          <t>택시운송사업 재정지원(자체)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>주차환경개선지원(평촌대로 일원 공영주차장 조성사업)</t>
+          <t>차량 고급화 보조</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>용현초등학교 일원 지중화사업</t>
+          <t>도로계획 및 관리 업무추진</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>반곡중 통학로 지중화</t>
+          <t>서광아파트 주변 도시계획도로 개설사업</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>농어촌도로정비사업</t>
+          <t>돌산읍 임포(시도1호선) 사면 복구</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>광양항 동서측 배후도로 보수공사</t>
+          <t>어린이 보호구역 조사 및 설계</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>특별교통수단도입보조(국비)</t>
+          <t>교통환경개선 및 안전시설물관리(주민참여예산 포함)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>내외국인 차량등록 관리</t>
+          <t>대중교통비 환급 지원</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>인력운영비(도로보수원)</t>
+          <t>기본경비(의창구 경제교통과)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>일광 동백마을 지구단위계획도로(소2-444호선) 개설</t>
+          <t>월평교차로구간 도로확장공사</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>월남동 영생아파트 부근 노인 교통사고 다발지역 개선</t>
+          <t>광교지구 도로 및 교통체계 개선대책 수립용역</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>무인교통단속장비 등 설치사업</t>
+          <t>대중교통지원</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>오포 능평리 국지도 57호선 방음시설 설치사업</t>
+          <t>지방도 기전시설 정비</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>온천교~온천장입구 교차로 도로확장공사</t>
+          <t>겨울철 제설대책 추진</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>전선 지중화 사업</t>
+          <t>장기미집행 도시계획시설 대지보상</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>버스터미널 환경개선(보조)</t>
+          <t>국도비 반환금</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>주차환경 개선</t>
+          <t>신호시스템 구축</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>골목길 LED보안등 개량</t>
+          <t>교량유지보수(보조)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>차량등록사업소운영</t>
+          <t>2025년 함평군 폭염저감시설 설치사업</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>매봉초 통학로 정비</t>
+          <t>공유재산(도로) 실태조사</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>전주·완주 시내버스 요금단일화 재정지원</t>
+          <t>보행로정비사업</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>복합커뮤니티센터 신축사업(생활문화센터,군민행복센터,공영주차장)</t>
+          <t>구 청사 주변 주차장 조성</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>[특별]위험교량 정비</t>
+          <t>도로포장관리시스템 구축운영(자체/직접)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>도로명주소 안내시설 설치사업</t>
+          <t>유구읍 백교·석남리(중로3-1호) 도시계획도로 개설</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>[국비]특별교통수단 구입지원</t>
+          <t>버스공영차고지 유지관리</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3016,17 +3016,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>위험도로 구조개선사업(고산 외율 위험도로 선형개량사업)(전환사업)</t>
+          <t>웅동지구 진입도로 개설사업(국가직접지원)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>농림해양수산</t>
+          <t>산업ㆍ중소기업및에너지</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>농업ㆍ농촌</t>
+          <t>산업ㆍ중소기업일반</t>
         </is>
       </c>
     </row>
@@ -3036,12 +3036,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>공영주차장 조성 및 유지보수</t>
+          <t>선우5차아파트 일원 인도정비공사</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>평창터미널 부지 및 건물 매입 사업</t>
+          <t>제5차 택시총량 조사</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>교통안전시설 확충(성인지)</t>
+          <t>지능형교통체계(ITS) 기본계획 수립 용역</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>홍농 산덕~하삼 도로 확포장</t>
+          <t>천포1리 전원타운 남편 도시계획도로(소2-1)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>버스정류장 개선사업(주민참여예산)</t>
+          <t>예비비(주차장 특별회계)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>보행가로 환경개선(주민참여예산)</t>
+          <t>부곡도시계획도로 개설 및 확포장</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>지하차도(터널), 육교승강기 유지관리(공사 위탁사업)</t>
+          <t>우동·중동 지역 도로정비</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>법인택시 운수종사자 처우개선</t>
+          <t>광역교통체계 인프라 조성</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>기배도시계획도로 소로2-A호선 개설공사</t>
+          <t>명곡도시계획도로(소2-26호선)개설</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>보개 기좌도로(소로1-1호선) 2구간 개설공사</t>
+          <t>영천미래형첨단복합도시진입도로개설</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>침산리 도시계획도로개설(소로3-174호)</t>
+          <t>보행자전용도로 수해복구</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>상기-내리간 도로확포장공사</t>
+          <t>광역도로(광주하남~장성삼계)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>도시계획도로 미지급용지 등 보상</t>
+          <t>풍무교 고가하부 상습침수구역 배수펌프 증설 공사 실시설계 용역</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>교통안전시설지원</t>
+          <t>태화강 그라스정원 노외 주차장 조성사업</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>논공 위천리 118번지선 도시계획도로 개설</t>
+          <t>초월읍 쌍동리(중로3-4호선) 도로개설공사</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>행복택시(수요응답형) 운영</t>
+          <t>벽오지 미운행 지역 벽지노선 지원사업</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>교통안전시설물 설치</t>
+          <t>미도아파트 앞 공영주차장 환경개선</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>시내버스 공공관리제 운영(자체/직접)</t>
+          <t>교통사고예방 횡단보도 안전조명등 설치 사업</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>자전거도로 및 이용시설물 정비</t>
+          <t>두룽산 등산로 주차장 조성</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>문화및관광</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>자연</t>
+          <t>관광</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>택시업계 재정지원</t>
+          <t>교통시설관리</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>택시 선진화 지원사업(브랜드콜택시)</t>
+          <t>공영주차장조성</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>남춘천교 보수보강</t>
+          <t>소음 유발 하수 뚜껑 교체 및 악취 발생 저감 사업</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>차로이탈경고장치 장착 보조(국고)</t>
+          <t>특별교통수단 도입비 지원</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>노후도로 재포장</t>
+          <t>도로보수 및 정비</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>도로명 및 건물번호 부여사업(보조)</t>
+          <t>도심보행네트워크 기반구축사업</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>호미반도 국가해양정원 예비타당성조사 용역&lt;보조&gt;</t>
+          <t>목포항 활성화</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>[도]지역현안도로사업</t>
+          <t>[도]위험도로구조개선(전환)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>도로변환경정비</t>
+          <t>도로제설</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>자전거 이용 활성화</t>
+          <t>택시요금 카드결제 수수료 지원</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3676,17 +3676,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>도로변 꽃길조성</t>
+          <t>[도]도민녹색자전거대행진행사지원</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>농림해양수산</t>
+          <t>문화및관광</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>임업ㆍ산촌</t>
+          <t>체육</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>메타버스 서울 추진</t>
+          <t>[도비]버스공공와이파이구축사업(국가직접지원)</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>공한지임시주차장조성</t>
+          <t>2019년 여객자동차터미널 정비사업</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>문화예술회관 남측 도로 정비공사</t>
+          <t>도로 재해예방 및 복구</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>교차로 운영체계 개선사업(보조)</t>
+          <t>인도설치 및 정비</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>노후 보안등주 교체 공사</t>
+          <t>도시계획도로 개설 및 개선(행구동 고문골길 인도(데크) 설치)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>백양로 보행환경개선사업</t>
+          <t>관내 노후 인도정비</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>신례2리(공천포선) 농어촌도로 315호선 확포장사업</t>
+          <t>농어촌도로(설105호선)도로선형개선공사</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>연지초교 통학로 지중화사업</t>
+          <t>고매IC 주변 도로 확포장[부담금사업]</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -3876,12 +3876,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>도로교통안전개선사업</t>
+          <t>직지대로(서청주IC~청주역) 확장</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -3896,12 +3896,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>농어촌버스 비수익노선 결손보전</t>
+          <t>대중교통비 환급 지원 사업(경남K-패스)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>도로명주소 기본도 유지보수사업</t>
+          <t>도로변 녹지정비</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>(국비보조)특별교통수단구입지원</t>
+          <t>주차장 관리 및 확보</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -3956,17 +3956,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>낭만버스커 거리문화공연 운영</t>
+          <t>전기차 보급 및 충전 인프라 구축</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>문화및관광</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>문화예술</t>
+          <t>환경보호일반</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>주차질서 계도</t>
+          <t>운수업체 유가보조금</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>시내버스 재정지원금</t>
+          <t>(도비보조)노후차선도색</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>교통및물류</t>
+          <t>수송및교통</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>전기 시내버스 구입 보조</t>
+          <t>대중교통 업무추진</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>인력운영비(주차장)</t>
+          <t>기본경비(덕진 산업교통과)</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>비법정도로개설</t>
+          <t>비법정도로 확포장</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>매송 도시계획도로 소로2-13호선 외 1개소 개설공사</t>
+          <t>홍천선(해미면 홍천리) 농어촌도로 확포장공사</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>택시 재정 지원</t>
+          <t>예비비</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>농어촌도로(원동 324호)개설공사</t>
+          <t>남면 무릉리 보행로 정비</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>교통질서 유지</t>
+          <t>가변적 주차허용(홀짝주정차제) 사업</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>도로유지 관리위탁</t>
+          <t>APEC대비 자전거도로 정비</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>무단방치 공유전동킥보드 단속 및 견인</t>
+          <t>도로조명설비 원격점검 인프라 구축사업</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2019년자전거도로정비</t>
+          <t>군도, 농어촌도로 유지보수사업</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>덕적 문갑리 어르너머고개 도로포장공사</t>
+          <t>지역현안도로(주민숙원)(도비)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>진천군 도로건설관리계획(변경) 수립 용역</t>
+          <t>7.16~20 호우피해 자력복구(농어촌도로)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>사북 도사곡교 재가설</t>
+          <t>도로정비 및 유지관리</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>영종·용유지역 도로청소</t>
+          <t>전기버스 보급</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>폐기물</t>
+          <t>대기</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>지방도 접도구역 관리</t>
+          <t>자전거도로관리</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>시비보조금 반환금(주차장특별회계)</t>
+          <t>수소충전소설치지원사업</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>일반공공행정</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>재정ㆍ금융</t>
+          <t>대기</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>충효 야척~재동간 도시계획도로 개설공사</t>
+          <t>도로명주소 홍보</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>(도)노후택시교체지원</t>
+          <t>보호구역 유지관리</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>고령운전자 운전면허 자진반납 활성화 사업(국고)</t>
+          <t>도로교통안전시설물 관련 송무수행</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>양촌 도시계획도로(소로2-9호선) 개설공사</t>
+          <t>부산진구 관내 침수예방공사</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>수송및교통</t>
+          <t>교통및물류</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>주차환경개선사업 공공주차장 이용보조</t>
+          <t>공촌천 보행환경 개선</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>산업ㆍ중소기업</t>
+          <t>국토및지역개발</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>산업진흥ㆍ고도화</t>
+          <t>수자원</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>화원 설화리(990-12번지선) 외 2개소 마을안길 정비</t>
+          <t>천성~외양포간 도로개설</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>송파공영차고지 정비 및 세차동 이전 공사</t>
+          <t>여좌동 공영주차장 조성(전환사업)</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4512,7 +4512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4523,7 +4523,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>CLAUDE.md 4장을 그대로 옮김 (분류 기준 v1.1)</t>
+          <t>CLAUDE.md 4장을 그대로 옮김</t>
         </is>
       </c>
       <c r="B1" s="4" t="n"/>
@@ -4532,7 +4532,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>## 4. 분류 기준 v1.1 (유일한 기준)</t>
+          <t>## 4. 분류 기준 v1.2 (유일한 기준, 2026-10-17 v1.1에서 개정, D23)</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>기존 도로 포장 보수·정비, 신호, 가드레일</t>
+          <t>기존 도로 포장 보수·정비, 신호, 가드레일, 기존 주차장 운영·관리</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>버스 지원·준공영제, 도시철도, 정류장, BRT, DRT, 환승</t>
+          <t>버스 지원·준공영제, 도시철도, 정류장, BRT, DRT, 환승, 공공형·수요응답형 택시, 섬 주민 여객선·도선 운항 지원</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>교통정보시스템, ITS, 교통 행정, 연구용역</t>
+          <t>교통정보시스템, ITS, 교통 행정, 연구용역, 주정차 단속, 일반 택시업계 지원</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>복합 사업 (판단 순서보다 먼저 적용):</t>
+          <t>재정 거래·택시·유가보조금 (판단 순서와 함께 적용):</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -4718,7 +4718,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>- 사업명에 여러 성격이 섞여 있으면, 사업비 대부분이 들어갈 주된 공사·지원 대상 하나만 보고 판단 순서를 적용한다.</t>
+          <t>- 재정 거래는 이동 수단에 쓴 돈이 아니므로 H: 다른 회계·기금으로 보내는 전출금, 기금 예탁·예치, 채무 원리금 상환, 보조금 반환·반납. (전출된 돈은 받은 회계에서 다시 사업비로 집계되어 중복 계상됨)</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -4727,7 +4727,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>- 보도·가로등·조경·부대시설처럼 주된 공사에 딸린 시설은 주된 대상으로 보지 않는다.</t>
+          <t>- 택시: 교통약자용(바우처택시, 장애인콜택시) → E / 대중교통 공백 지역을 대신하는 공공형·수요응답형 택시(희망택시, 100원택시 등) → C / 그 밖의 택시업계 지원(유가보조금, 감차 보상, 운수종사자 지원, 택시 행정) → G</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -4736,44 +4736,44 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>- 예: "○○로 확장 및 보도 설치" → A / "○○동 보행환경 개선(노면 재포장 포함)" → D</t>
+          <t>- 유가보조금: 화물 → H / 버스 → C / 택시 → G / 사업명으로 대상을 알 수 없으면 H, 확신도 low</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
       <c r="C18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>- 주된 대상을 가릴 수 없으면 확신도 low.</t>
-        </is>
-      </c>
+      <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="4" t="n"/>
       <c r="C19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr"/>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>복합 사업 (판단 순서보다 먼저 적용):</t>
+        </is>
+      </c>
       <c r="B20" s="4" t="n"/>
       <c r="C20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>판단 순서 (위에서부터 먼저 해당하는 것으로 결정. 사람 라벨링과 LLM 모두 동일):</t>
-        </is>
-      </c>
+      <c r="A21" s="4" t="inlineStr"/>
       <c r="B21" s="4" t="n"/>
       <c r="C21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr"/>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>- 사업명에 여러 성격이 섞여 있으면, 사업비 대부분이 들어갈 주된 공사·지원 대상 하나만 보고 판단 순서를 적용한다.</t>
+        </is>
+      </c>
       <c r="B22" s="4" t="n"/>
       <c r="C22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>1. 이동 수단과 무관, 공원·하천 내부 여가시설(공원 안 산책로·보행로 포함), 항만·공항·화물물류 → H</t>
+          <t>- 보도·가로등·조경·부대시설처럼 주된 공사에 딸린 시설은 주된 대상으로 보지 않는다.</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -4782,7 +4782,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2. 교통약자 대상 → E (저상버스 포함)</t>
+          <t>- 예: "○○로 확장 및 보도 설치" → A / "○○동 보행환경 개선(노면 재포장 포함)" → D</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -4791,43 +4791,35 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3. 보행자·자전거 대상 → D (보행자 보호 목적의 안전사업 포함)</t>
+          <t>- 주된 대상을 가릴 수 없으면 확신도 low.</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
       <c r="C25" s="4" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>4. 대중교통 → C</t>
-        </is>
-      </c>
+      <c r="A26" s="4" t="inlineStr"/>
       <c r="B26" s="4" t="n"/>
       <c r="C26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>5. 차량 연료 전환 → F</t>
+          <t>판단 순서 (위에서부터 먼저 해당하는 것으로 결정. 사람 라벨링과 LLM 모두 동일):</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
       <c r="C27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>6. 신설·확장·개설·4차로화 → A</t>
-        </is>
-      </c>
+      <c r="A28" s="4" t="inlineStr"/>
       <c r="B28" s="4" t="n"/>
       <c r="C28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>7. 기존 도로 관리·차량 안전 → B</t>
+          <t>1. 이동 수단과 무관, 공원·하천 내부 여가시설(공원 안 산책로·보행로 포함), 항만·공항 시설, 화물물류, 재정 거래 → H</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -4836,7 +4828,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>8. 시스템·행정·용역 → G</t>
+          <t>2. 교통약자 대상 → E (저상버스 포함)</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -4845,25 +4837,102 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>9. 사업명만으로 확신 불가 → H, 확신도 low</t>
+          <t>3. 보행자·자전거 대상 → D (보행자 보호 목적의 안전사업 포함)</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
       <c r="C31" s="4" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr"/>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>4. 대중교통 → C (공공형 택시, 섬 주민 여객선·도선 운항 지원 포함)</t>
+        </is>
+      </c>
       <c r="B32" s="4" t="n"/>
       <c r="C32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>확신도 표기: high / low (사람 라벨과 LLM 동일)</t>
+          <t>5. 차량 연료 전환 → F</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
       <c r="C33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>6. 신설·확장·개설·4차로화 → A</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>7. 기존 도로 관리·차량 안전 → B</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>8. 시스템·행정·용역 → G (일반 택시업계 지원 포함)</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>9. 교통 사업인지, 무슨 사업인지 사업명만으로 알 수 없음 → H, 확신도 low</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>확신도 (사람 라벨과 LLM 동일):</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>- high: 사업명에서 대상(버스, 보도 등)이나 공사 종류(신설, 확장, 재포장 등)가 드러나 범주가 하나로 정해질 때</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>- low: 두 범주 사이에서 고민될 때. 이때는 H로 보내지 말고 더 가능성 높은 범주를 고른다. 사업 내용 자체를 알 수 없을 때만 9번에 따라 H, low</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
